--- a/astro-site/public/dl/kit-tareas-heladeria/06-eventos-temporada.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/06-eventos-temporada.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Temporada Alta" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Temporada Baja" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Catering Eventos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Alta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temporada Baja" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering Eventos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Temporada Alta'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Temporada Baja'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Catering Eventos'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -157,60 +166,71 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -570,15 +590,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -586,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -621,9 +643,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -645,8 +665,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -655,18 +692,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,6 +720,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -822,6 +860,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -979,6 +1018,26 @@
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(E6:E19,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>COUNTIF(B6:B19,"?*")</f>
+        <v>12.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
@@ -1003,12 +1062,26 @@
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1017,18 +1090,18 @@
   <sheetPr>
     <tabColor rgb="00E0F7FA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1045,6 +1118,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1165,6 +1239,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1303,6 +1378,26 @@
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(E6:E17,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(B6:B17,"?*")</f>
+        <v>10.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
@@ -1327,12 +1422,26 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G17">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1341,18 +1450,18 @@
   <sheetPr>
     <tabColor rgb="00F3E5F5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1369,6 +1478,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1489,6 +1599,7 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -1590,6 +1701,7 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
@@ -1709,6 +1821,26 @@
       <c r="E22" s="12" t="n"/>
       <c r="F22" s="11" t="n"/>
       <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C23">
+        <f>COUNTIF(E6:E22,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E23">
+        <f>COUNTIF(B6:B22,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
@@ -1734,11 +1866,25 @@
     <mergeCell ref="A24:G24"/>
     <mergeCell ref="A11:G11"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G22">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-heladeria/06-eventos-temporada.xlsx
+++ b/astro-site/public/dl/kit-tareas-heladeria/06-eventos-temporada.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -667,9 +667,38 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Antes de aceptar un evento:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ La primera sección de «Catering Eventos» es lo que se pacta ANTES de producir: alérgenos por escrito, nº de comensales, precio, señal y condiciones de cancelación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Pide siempre señal: el helado de un evento se produce a medida y, si el evento se cae, no se revende.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-heladeria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1026,8 +1055,8 @@
         </is>
       </c>
       <c r="C20">
-        <f>COUNTIF(E6:E19,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B19,"?*",E6:E19,"✓")-COUNTIFS(B6:B19,"Tarea",E6:E19,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1035,8 +1064,8 @@
         </is>
       </c>
       <c r="E20">
-        <f>COUNTIF(B6:B19,"?*")</f>
-        <v>12.0</v>
+        <f>COUNTIF(B6:B19,"?*")-COUNTIF(B6:B19,"Tarea")-COUNTIF(E6:E19,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
     <row r="21">
@@ -1068,8 +1097,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1386,8 +1415,8 @@
         </is>
       </c>
       <c r="C18">
-        <f>COUNTIF(E6:E17,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B17,"?*",E6:E17,"✓")-COUNTIFS(B6:B17,"Tarea",E6:E17,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1395,8 +1424,8 @@
         </is>
       </c>
       <c r="E18">
-        <f>COUNTIF(B6:B17,"?*")</f>
-        <v>10.0</v>
+        <f>COUNTIF(B6:B17,"?*")-COUNTIF(B6:B17,"Tarea")-COUNTIF(E6:E17,"N/A")</f>
+        <v>9.0</v>
       </c>
     </row>
     <row r="19">
@@ -1428,8 +1457,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E16 E17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1452,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1482,7 +1511,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Preparación del evento</t>
+          <t>Al confirmar el pedido o el evento</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1558,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Diseñar carta catering: formatos (bola, vasito, tarrina mini, tarta helada)</t>
+          <t>Recoger POR ESCRITO los alérgenos e intolerancias de los comensales y confirmar qué sabores puedes servir: una carta de heladería concentra LECHE, FRUTOS SECOS, HUEVO, GLUTEN (barquillo y galleta), SOJA y SULFITOS</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1548,12 +1577,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Calcular producción: 2-3 bolas/persona, mínimo 4 sabores</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Confirmar por escrito nº de comensales, formatos, hora y lugar del servicio, y quién recibe el material en el sitio</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -1567,12 +1596,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Producir con 24-48h de antelación y almacenar a -18°C</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Obrador</t>
+          <t>Fijar el precio por comensal (o por kg) y cobrar SEÑAL antes de producir: el helado se hace a medida y no se revende</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -1586,12 +1615,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Preparar kit de servicio externo: cubetas, espátulas, guantes, servilletas</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Logística</t>
+          <t>Acordar por escrito las condiciones de cancelación y hasta cuándo se puede cambiar el número de comensales</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -1599,82 +1628,84 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="13" t="n"/>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que hay hueco en cámara a −18 °C para todo el pedido ANTES de aceptarlo</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="13" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Logística y transporte</t>
-        </is>
-      </c>
+      <c r="A11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Preparación del evento</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Verificar cadena de frío para transporte (cajas isotérmicas, hielo seco)</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Cargar vehículo con producto y material de servicio</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Logística</t>
+          <t>Diseñar carta catering: formatos (bola, vasito, tarrina mini, tarta helada)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D14" s="11" t="n"/>
@@ -1684,16 +1715,16 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperatura de producto a la llegada (&lt;-12°C)</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Logística</t>
+          <t>Calcular producción: 2-3 bolas/persona, mínimo 4 sabores</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D15" s="11" t="n"/>
@@ -1701,96 +1732,96 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="13" t="n"/>
     </row>
-    <row r="16"/>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Producir con 24-48h de antelación y almacenar a −18 °C</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="13" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Servicio y cierre</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A17" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Preparar kit de servicio externo: cubetas, espátulas, guantes, servilletas</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Logística y transporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Montar mesa de servicio en el evento según briefing del cliente</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="13" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Servir helado manteniendo presentación y rotación de sabores</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Servicio</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="13" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Recoger material, limpiar zona y transportar de vuelta</t>
+          <t>Verificar cadena de frío para transporte (cajas isotérmicas, hielo seco)</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -1805,16 +1836,16 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Emitir factura y enviar encuesta de satisfacción al cliente</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Cargar vehículo con producto y material de servicio</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D22" s="11" t="n"/>
@@ -1823,57 +1854,198 @@
       <c r="G22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="A23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Verificar la temperatura del producto a la llegada (≤ −12 °C) — anota la lectura: ____ °C. Por encima, no lo sirvas: valóralo antes</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Servicio y cierre</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Montar mesa de servicio en el evento según briefing del cliente</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Servir helado manteniendo presentación y rotación de sabores</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Servicio</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Recoger material, limpiar zona y transportar de vuelta</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Emitir factura y enviar encuesta de satisfacción al cliente</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C23">
-        <f>COUNTIF(E6:E22,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C31">
+        <f>COUNTIFS(B6:B30,"?*",E6:E30,"✓")-COUNTIFS(B6:B30,"Tarea",E6:E30,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E23">
-        <f>COUNTIF(B6:B22,"?*")</f>
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="E31">
+        <f>COUNTIF(B6:B30,"?*")-COUNTIF(B6:B30,"Tarea")-COUNTIF(E6:E30,"N/A")</f>
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G22">
+  <conditionalFormatting sqref="A6:G30">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E13 E14 E15 E19 E20 E21 E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E21 E22 E23 E27 E28 E29 E30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
